--- a/branch_region_mapping.xlsx
+++ b/branch_region_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe345492276495d5/Desktop/dashboard 5/Google_review_EI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{EE4C7F99-E6C3-4957-80F9-5924202B6A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70A93645-7A05-4B16-9B03-9B603C9C455E}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{EE4C7F99-E6C3-4957-80F9-5924202B6A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B51F60A2-7D33-4C86-9F1F-41E739AC98BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>branch_flag</t>
   </si>
@@ -148,6 +148,15 @@
   </si>
   <si>
     <t>EI - Fujairah - Fujairah Branch</t>
+  </si>
+  <si>
+    <t>EI - Dubai - Healthcare City Home Finance Center</t>
+  </si>
+  <si>
+    <t>EI - Dubai - Nad Al Hamar Home Finance Center</t>
+  </si>
+  <si>
+    <t>EI - Sharjah - Qasimiyah Home Finance Center</t>
   </si>
 </sst>
 </file>
@@ -223,6 +232,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60.109375" bestFit="1" customWidth="1"/>
@@ -774,6 +787,30 @@
         <v>3</v>
       </c>
     </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
